--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ66"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3467,48 +3467,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124754565</v>
+        <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>782246</v>
+        <v>782379</v>
       </c>
       <c r="R29" t="n">
-        <v>7290419</v>
+        <v>7290686</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3532,12 +3532,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3563,13 +3573,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754565</t>
+          <t>https://artportalen.se/Sighting/136898208</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124754566</v>
+        <v>124754565</v>
       </c>
       <c r="B30" t="n">
         <v>79084</v>
@@ -3604,10 +3614,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>782169</v>
+        <v>782246</v>
       </c>
       <c r="R30" t="n">
-        <v>7290528</v>
+        <v>7290419</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3665,13 +3675,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754566</t>
+          <t>https://artportalen.se/Sighting/124754565</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124754567</v>
+        <v>124754566</v>
       </c>
       <c r="B31" t="n">
         <v>79084</v>
@@ -3706,10 +3716,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>782118</v>
+        <v>782169</v>
       </c>
       <c r="R31" t="n">
-        <v>7290718</v>
+        <v>7290528</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3767,13 +3777,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754567</t>
+          <t>https://artportalen.se/Sighting/124754566</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124754568</v>
+        <v>124754567</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -3811,7 +3821,7 @@
         <v>782118</v>
       </c>
       <c r="R32" t="n">
-        <v>7290721</v>
+        <v>7290718</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,11 +3856,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3874,16 +3879,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754568</t>
+          <t>https://artportalen.se/Sighting/124754567</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124633208</v>
+        <v>124754568</v>
       </c>
       <c r="B33" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,21 +3896,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3915,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>782282</v>
+        <v>782118</v>
       </c>
       <c r="R33" t="n">
-        <v>7290386</v>
+        <v>7290721</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3945,12 +3950,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3976,13 +3986,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633208</t>
+          <t>https://artportalen.se/Sighting/124754568</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124633209</v>
+        <v>124633208</v>
       </c>
       <c r="B34" t="n">
         <v>79946</v>
@@ -4017,10 +4027,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>782110</v>
+        <v>782282</v>
       </c>
       <c r="R34" t="n">
-        <v>7290605</v>
+        <v>7290386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4078,13 +4088,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633209</t>
+          <t>https://artportalen.se/Sighting/124633208</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124754546</v>
+        <v>124633209</v>
       </c>
       <c r="B35" t="n">
         <v>79946</v>
@@ -4119,10 +4129,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>782162</v>
+        <v>782110</v>
       </c>
       <c r="R35" t="n">
-        <v>7290539</v>
+        <v>7290605</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4149,17 +4159,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Silverstubbe delvis nedbruten</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4185,13 +4190,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754546</t>
+          <t>https://artportalen.se/Sighting/124633209</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124791537</v>
+        <v>124754546</v>
       </c>
       <c r="B36" t="n">
         <v>79946</v>
@@ -4222,14 +4227,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>782155</v>
+        <v>782162</v>
       </c>
       <c r="R36" t="n">
-        <v>7290552</v>
+        <v>7290539</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,6 +4269,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Silverstubbe delvis nedbruten</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4276,24 +4286,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791537</t>
+          <t>https://artportalen.se/Sighting/124754546</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125141668</v>
+        <v>124791537</v>
       </c>
       <c r="B37" t="n">
         <v>79946</v>
@@ -4324,14 +4334,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>782209</v>
+        <v>782155</v>
       </c>
       <c r="R37" t="n">
-        <v>7290451</v>
+        <v>7290552</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4378,24 +4388,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125141668</t>
+          <t>https://artportalen.se/Sighting/124791537</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125141670</v>
+        <v>125141668</v>
       </c>
       <c r="B38" t="n">
         <v>79946</v>
@@ -4430,10 +4440,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>782114</v>
+        <v>782209</v>
       </c>
       <c r="R38" t="n">
-        <v>7290605</v>
+        <v>7290451</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4491,16 +4501,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125141670</t>
+          <t>https://artportalen.se/Sighting/125141668</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118904723</v>
+        <v>125141670</v>
       </c>
       <c r="B39" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4508,34 +4518,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gängesmyran, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>782143</v>
+        <v>782114</v>
       </c>
       <c r="R39" t="n">
-        <v>7290492</v>
+        <v>7290605</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4562,22 +4572,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4603,13 +4603,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118904723</t>
+          <t>https://artportalen.se/Sighting/125141670</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125061502</v>
+        <v>118904723</v>
       </c>
       <c r="B40" t="n">
         <v>80432</v>
@@ -4640,14 +4640,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>782402</v>
+        <v>782143</v>
       </c>
       <c r="R40" t="n">
-        <v>7290733</v>
+        <v>7290492</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4674,17 +4674,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4699,49 +4704,49 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125061502</t>
+          <t>https://artportalen.se/Sighting/118904723</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124791543</v>
+        <v>125061502</v>
       </c>
       <c r="B41" t="n">
-        <v>57950</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4751,10 +4756,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>782450</v>
+        <v>782402</v>
       </c>
       <c r="R41" t="n">
-        <v>7290515</v>
+        <v>7290733</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4781,17 +4786,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4817,16 +4822,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791543</t>
+          <t>https://artportalen.se/Sighting/125061502</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124633210</v>
+        <v>124791543</v>
       </c>
       <c r="B42" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4834,34 +4839,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>782119</v>
+        <v>782450</v>
       </c>
       <c r="R42" t="n">
-        <v>7290637</v>
+        <v>7290515</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4888,12 +4893,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4908,27 +4918,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633210</t>
+          <t>https://artportalen.se/Sighting/124791543</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124791551</v>
+        <v>124633210</v>
       </c>
       <c r="B43" t="n">
-        <v>57132</v>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4936,39 +4946,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>782135</v>
+        <v>782119</v>
       </c>
       <c r="R43" t="n">
         <v>7290637</v>
@@ -4998,12 +5000,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5018,27 +5020,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791551</t>
+          <t>https://artportalen.se/Sighting/124633210</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124754558</v>
+        <v>124791551</v>
       </c>
       <c r="B44" t="n">
-        <v>57144</v>
+        <v>57132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5046,16 +5048,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5064,16 +5066,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>782163</v>
+        <v>782135</v>
       </c>
       <c r="R44" t="n">
-        <v>7290484</v>
+        <v>7290637</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5108,11 +5118,6 @@
           <t>2025-05-04</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>tömmning</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5125,27 +5130,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754558</t>
+          <t>https://artportalen.se/Sighting/124791551</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125060607</v>
+        <v>124754558</v>
       </c>
       <c r="B45" t="n">
-        <v>58327</v>
+        <v>57144</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5153,16 +5158,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5171,24 +5176,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>782418</v>
+        <v>782163</v>
       </c>
       <c r="R45" t="n">
-        <v>7290732</v>
+        <v>7290484</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,12 +5212,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>tömmning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5235,24 +5237,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125060607</t>
+          <t>https://artportalen.se/Sighting/124754558</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125061503</v>
+        <v>125060607</v>
       </c>
       <c r="B46" t="n">
         <v>58327</v>
@@ -5295,10 +5297,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>782223</v>
+        <v>782418</v>
       </c>
       <c r="R46" t="n">
-        <v>7290430</v>
+        <v>7290732</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5325,12 +5327,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5356,38 +5358,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125061503</t>
+          <t>https://artportalen.se/Sighting/125060607</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124640958</v>
+        <v>125061503</v>
       </c>
       <c r="B47" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5395,7 +5397,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5405,10 +5407,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>782338</v>
+        <v>782223</v>
       </c>
       <c r="R47" t="n">
-        <v>7290449</v>
+        <v>7290430</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5435,12 +5437,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5466,56 +5468,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124640958</t>
+          <t>https://artportalen.se/Sighting/125061503</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118904060</v>
+        <v>124640958</v>
       </c>
       <c r="B48" t="n">
-        <v>56884</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>208255</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gängesmyran, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>782143</v>
+        <v>782338</v>
       </c>
       <c r="R48" t="n">
-        <v>7290492</v>
+        <v>7290449</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5542,22 +5547,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5566,69 +5561,73 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118904060</t>
+          <t>https://artportalen.se/Sighting/124640958</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119416285</v>
+        <v>118904060</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>56884</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>208255</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Asplövberg, Nb</t>
+          <t>Gängesmyran, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>782416</v>
+        <v>782143</v>
       </c>
       <c r="R49" t="n">
-        <v>7290528</v>
+        <v>7290492</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5655,12 +5654,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5669,30 +5678,31 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119416285</t>
+          <t>https://artportalen.se/Sighting/118904060</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124754569</v>
+        <v>119416285</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -5723,14 +5733,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>782394</v>
+        <v>782416</v>
       </c>
       <c r="R50" t="n">
-        <v>7290494</v>
+        <v>7290528</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5757,12 +5767,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5777,24 +5787,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754569</t>
+          <t>https://artportalen.se/Sighting/119416285</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124754570</v>
+        <v>124754569</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -5829,10 +5839,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>782395</v>
+        <v>782394</v>
       </c>
       <c r="R51" t="n">
-        <v>7290480</v>
+        <v>7290494</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5890,13 +5900,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754570</t>
+          <t>https://artportalen.se/Sighting/124754569</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124791547</v>
+        <v>124754570</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -5927,14 +5937,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>782387</v>
+        <v>782395</v>
       </c>
       <c r="R52" t="n">
-        <v>7290599</v>
+        <v>7290480</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5981,24 +5991,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791547</t>
+          <t>https://artportalen.se/Sighting/124754570</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124791548</v>
+        <v>124791547</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6033,10 +6043,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>782384</v>
+        <v>782387</v>
       </c>
       <c r="R53" t="n">
-        <v>7290574</v>
+        <v>7290599</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,13 +6104,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791548</t>
+          <t>https://artportalen.se/Sighting/124791547</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124791549</v>
+        <v>124791548</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6135,10 +6145,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>782377</v>
+        <v>782384</v>
       </c>
       <c r="R54" t="n">
-        <v>7290562</v>
+        <v>7290574</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6196,51 +6206,51 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791549</t>
+          <t>https://artportalen.se/Sighting/124791548</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124633215</v>
+        <v>124791549</v>
       </c>
       <c r="B55" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>782074</v>
+        <v>782377</v>
       </c>
       <c r="R55" t="n">
-        <v>7290847</v>
+        <v>7290562</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6267,12 +6277,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6287,24 +6297,24 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633215</t>
+          <t>https://artportalen.se/Sighting/124791549</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124640962</v>
+        <v>124633215</v>
       </c>
       <c r="B56" t="n">
         <v>97983</v>
@@ -6335,14 +6345,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>782138</v>
+        <v>782074</v>
       </c>
       <c r="R56" t="n">
-        <v>7290753</v>
+        <v>7290847</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6389,24 +6399,24 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124640962</t>
+          <t>https://artportalen.se/Sighting/124633215</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124754557</v>
+        <v>124640962</v>
       </c>
       <c r="B57" t="n">
         <v>97983</v>
@@ -6437,14 +6447,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>782122</v>
+        <v>782138</v>
       </c>
       <c r="R57" t="n">
-        <v>7290733</v>
+        <v>7290753</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6471,12 +6481,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6491,27 +6501,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754557</t>
+          <t>https://artportalen.se/Sighting/124640962</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118904523</v>
+        <v>124754557</v>
       </c>
       <c r="B58" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6519,34 +6529,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gängesmyran, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>782143</v>
+        <v>782122</v>
       </c>
       <c r="R58" t="n">
-        <v>7290492</v>
+        <v>7290733</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6573,22 +6583,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6614,51 +6614,51 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118904523</t>
+          <t>https://artportalen.se/Sighting/124754557</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124633218</v>
+        <v>118904523</v>
       </c>
       <c r="B59" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>782284</v>
+        <v>782143</v>
       </c>
       <c r="R59" t="n">
-        <v>7290387</v>
+        <v>7290492</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6685,12 +6685,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6716,13 +6726,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633218</t>
+          <t>https://artportalen.se/Sighting/118904523</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124754560</v>
+        <v>124633218</v>
       </c>
       <c r="B60" t="n">
         <v>79085</v>
@@ -6757,10 +6767,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>782118</v>
+        <v>782284</v>
       </c>
       <c r="R60" t="n">
-        <v>7290721</v>
+        <v>7290387</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6787,17 +6797,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6823,13 +6828,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754560</t>
+          <t>https://artportalen.se/Sighting/124633218</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124754561</v>
+        <v>124754560</v>
       </c>
       <c r="B61" t="n">
         <v>79085</v>
@@ -6864,10 +6869,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>782174</v>
+        <v>782118</v>
       </c>
       <c r="R61" t="n">
-        <v>7290529</v>
+        <v>7290721</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6902,6 +6907,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6925,16 +6935,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754561</t>
+          <t>https://artportalen.se/Sighting/124754560</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124791539</v>
+        <v>124754561</v>
       </c>
       <c r="B62" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6942,34 +6952,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>782511</v>
+        <v>782174</v>
       </c>
       <c r="R62" t="n">
-        <v>7290463</v>
+        <v>7290529</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7016,24 +7026,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791539</t>
+          <t>https://artportalen.se/Sighting/124754561</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124791540</v>
+        <v>124791539</v>
       </c>
       <c r="B63" t="n">
         <v>79917</v>
@@ -7068,10 +7078,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>782565</v>
+        <v>782511</v>
       </c>
       <c r="R63" t="n">
-        <v>7290181</v>
+        <v>7290463</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7129,13 +7139,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791540</t>
+          <t>https://artportalen.se/Sighting/124791539</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125141672</v>
+        <v>124791540</v>
       </c>
       <c r="B64" t="n">
         <v>79917</v>
@@ -7166,14 +7176,14 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>782114</v>
+        <v>782565</v>
       </c>
       <c r="R64" t="n">
-        <v>7290605</v>
+        <v>7290181</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7220,24 +7230,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125141672</t>
+          <t>https://artportalen.se/Sighting/124791540</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125141673</v>
+        <v>125141672</v>
       </c>
       <c r="B65" t="n">
         <v>79917</v>
@@ -7272,10 +7282,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>782137</v>
+        <v>782114</v>
       </c>
       <c r="R65" t="n">
-        <v>7290681</v>
+        <v>7290605</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7333,16 +7343,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125141673</t>
+          <t>https://artportalen.se/Sighting/125141672</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124754554</v>
+        <v>125141673</v>
       </c>
       <c r="B66" t="n">
-        <v>79350</v>
+        <v>79917</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7350,21 +7360,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7374,10 +7384,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>782326</v>
+        <v>782137</v>
       </c>
       <c r="R66" t="n">
-        <v>7290301</v>
+        <v>7290681</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7434,6 +7444,108 @@
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125141673</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>124754554</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>782326</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7290301</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124754554</t>
         </is>
@@ -7506,6 +7618,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ67"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4935,48 +4935,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124633210</v>
+        <v>137247075</v>
       </c>
       <c r="B43" t="n">
-        <v>57141</v>
+        <v>58023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>782119</v>
+        <v>782380</v>
       </c>
       <c r="R43" t="n">
-        <v>7290637</v>
+        <v>7290687</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5000,12 +5000,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5020,44 +5035,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633210</t>
+          <t>https://artportalen.se/Sighting/137247075</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124791551</v>
+        <v>137247076</v>
       </c>
       <c r="B44" t="n">
-        <v>57132</v>
+        <v>58023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5066,27 +5081,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>782135</v>
+        <v>782372</v>
       </c>
       <c r="R44" t="n">
-        <v>7290637</v>
+        <v>7290682</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5110,12 +5117,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5130,27 +5152,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791551</t>
+          <t>https://artportalen.se/Sighting/137247076</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124754558</v>
+        <v>124633210</v>
       </c>
       <c r="B45" t="n">
-        <v>57144</v>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5158,21 +5180,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5182,10 +5204,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>782163</v>
+        <v>782119</v>
       </c>
       <c r="R45" t="n">
-        <v>7290484</v>
+        <v>7290637</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5212,17 +5234,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>tömmning</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5248,16 +5265,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754558</t>
+          <t>https://artportalen.se/Sighting/124633210</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125060607</v>
+        <v>124791551</v>
       </c>
       <c r="B46" t="n">
-        <v>58327</v>
+        <v>57132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5265,16 +5282,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5287,7 +5304,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5297,10 +5314,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>782418</v>
+        <v>782135</v>
       </c>
       <c r="R46" t="n">
-        <v>7290732</v>
+        <v>7290637</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5327,12 +5344,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5358,16 +5375,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125060607</t>
+          <t>https://artportalen.se/Sighting/124791551</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125061503</v>
+        <v>124754558</v>
       </c>
       <c r="B47" t="n">
-        <v>58327</v>
+        <v>57144</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5375,16 +5392,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5393,24 +5410,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>782223</v>
+        <v>782163</v>
       </c>
       <c r="R47" t="n">
-        <v>7290430</v>
+        <v>7290484</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5445,6 +5454,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>tömmning</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5457,49 +5471,49 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125061503</t>
+          <t>https://artportalen.se/Sighting/124754558</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124640958</v>
+        <v>125060607</v>
       </c>
       <c r="B48" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5507,7 +5521,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5517,10 +5531,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>782338</v>
+        <v>782418</v>
       </c>
       <c r="R48" t="n">
-        <v>7290449</v>
+        <v>7290732</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5547,12 +5561,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5578,16 +5592,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124640958</t>
+          <t>https://artportalen.se/Sighting/125060607</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118904060</v>
+        <v>125061503</v>
       </c>
       <c r="B49" t="n">
-        <v>56884</v>
+        <v>58327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5595,39 +5609,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>208255</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gängesmyran, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>782143</v>
+        <v>782223</v>
       </c>
       <c r="R49" t="n">
-        <v>7290492</v>
+        <v>7290430</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5654,22 +5671,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5678,69 +5685,76 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118904060</t>
+          <t>https://artportalen.se/Sighting/125061503</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119416285</v>
+        <v>124640958</v>
       </c>
       <c r="B50" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>782416</v>
+        <v>782338</v>
       </c>
       <c r="R50" t="n">
-        <v>7290528</v>
+        <v>7290449</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5767,12 +5781,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5798,51 +5812,56 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119416285</t>
+          <t>https://artportalen.se/Sighting/124640958</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124754569</v>
+        <v>118904060</v>
       </c>
       <c r="B51" t="n">
-        <v>99118</v>
+        <v>56884</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>208255</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>782394</v>
+        <v>782143</v>
       </c>
       <c r="R51" t="n">
-        <v>7290494</v>
+        <v>7290492</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5869,12 +5888,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5883,6 +5912,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5900,13 +5930,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754569</t>
+          <t>https://artportalen.se/Sighting/118904060</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124754570</v>
+        <v>119416285</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -5937,14 +5967,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>782395</v>
+        <v>782416</v>
       </c>
       <c r="R52" t="n">
-        <v>7290480</v>
+        <v>7290528</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5971,12 +6001,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5991,24 +6021,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754570</t>
+          <t>https://artportalen.se/Sighting/119416285</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124791547</v>
+        <v>124754569</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6039,14 +6069,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>782387</v>
+        <v>782394</v>
       </c>
       <c r="R53" t="n">
-        <v>7290599</v>
+        <v>7290494</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6093,24 +6123,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791547</t>
+          <t>https://artportalen.se/Sighting/124754569</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124791548</v>
+        <v>124754570</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6141,14 +6171,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>782384</v>
+        <v>782395</v>
       </c>
       <c r="R54" t="n">
-        <v>7290574</v>
+        <v>7290480</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6195,24 +6225,24 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791548</t>
+          <t>https://artportalen.se/Sighting/124754570</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124791549</v>
+        <v>124791547</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6247,10 +6277,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>782377</v>
+        <v>782387</v>
       </c>
       <c r="R55" t="n">
-        <v>7290562</v>
+        <v>7290599</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6308,51 +6338,51 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791549</t>
+          <t>https://artportalen.se/Sighting/124791547</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124633215</v>
+        <v>124791548</v>
       </c>
       <c r="B56" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>782074</v>
+        <v>782384</v>
       </c>
       <c r="R56" t="n">
-        <v>7290847</v>
+        <v>7290574</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6379,12 +6409,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6399,49 +6429,49 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633215</t>
+          <t>https://artportalen.se/Sighting/124791548</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124640962</v>
+        <v>124791549</v>
       </c>
       <c r="B57" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6451,10 +6481,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>782138</v>
+        <v>782377</v>
       </c>
       <c r="R57" t="n">
-        <v>7290753</v>
+        <v>7290562</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6481,12 +6511,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6512,13 +6542,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124640962</t>
+          <t>https://artportalen.se/Sighting/124791549</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124754557</v>
+        <v>124633215</v>
       </c>
       <c r="B58" t="n">
         <v>97983</v>
@@ -6553,10 +6583,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>782122</v>
+        <v>782074</v>
       </c>
       <c r="R58" t="n">
-        <v>7290733</v>
+        <v>7290847</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6583,12 +6613,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6614,16 +6644,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754557</t>
+          <t>https://artportalen.se/Sighting/124633215</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118904523</v>
+        <v>124640962</v>
       </c>
       <c r="B59" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6631,34 +6661,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gängesmyran, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>782143</v>
+        <v>782138</v>
       </c>
       <c r="R59" t="n">
-        <v>7290492</v>
+        <v>7290753</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6685,22 +6715,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6715,49 +6735,49 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118904523</t>
+          <t>https://artportalen.se/Sighting/124640962</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124633218</v>
+        <v>124754557</v>
       </c>
       <c r="B60" t="n">
-        <v>79085</v>
+        <v>97983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6767,10 +6787,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>782284</v>
+        <v>782122</v>
       </c>
       <c r="R60" t="n">
-        <v>7290387</v>
+        <v>7290733</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6797,12 +6817,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6828,51 +6848,51 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124633218</t>
+          <t>https://artportalen.se/Sighting/124754557</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124754560</v>
+        <v>118904523</v>
       </c>
       <c r="B61" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>782118</v>
+        <v>782143</v>
       </c>
       <c r="R61" t="n">
-        <v>7290721</v>
+        <v>7290492</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6899,17 +6919,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6935,13 +6960,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754560</t>
+          <t>https://artportalen.se/Sighting/118904523</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124754561</v>
+        <v>124633218</v>
       </c>
       <c r="B62" t="n">
         <v>79085</v>
@@ -6976,10 +7001,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>782174</v>
+        <v>782284</v>
       </c>
       <c r="R62" t="n">
-        <v>7290529</v>
+        <v>7290387</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7006,12 +7031,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7037,16 +7062,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124754561</t>
+          <t>https://artportalen.se/Sighting/124633218</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124791539</v>
+        <v>124754560</v>
       </c>
       <c r="B63" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7054,34 +7079,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>782511</v>
+        <v>782118</v>
       </c>
       <c r="R63" t="n">
-        <v>7290463</v>
+        <v>7290721</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7116,6 +7141,11 @@
           <t>2025-05-04</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7128,27 +7158,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791539</t>
+          <t>https://artportalen.se/Sighting/124754560</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124791540</v>
+        <v>124754561</v>
       </c>
       <c r="B64" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7156,34 +7186,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberget, Nb</t>
+          <t>Gängesmyran Asplövberg, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>782565</v>
+        <v>782174</v>
       </c>
       <c r="R64" t="n">
-        <v>7290181</v>
+        <v>7290529</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7230,24 +7260,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124791540</t>
+          <t>https://artportalen.se/Sighting/124754561</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125141672</v>
+        <v>124791539</v>
       </c>
       <c r="B65" t="n">
         <v>79917</v>
@@ -7278,14 +7308,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>782114</v>
+        <v>782511</v>
       </c>
       <c r="R65" t="n">
-        <v>7290605</v>
+        <v>7290463</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7332,24 +7362,24 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125141672</t>
+          <t>https://artportalen.se/Sighting/124791539</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125141673</v>
+        <v>124791540</v>
       </c>
       <c r="B66" t="n">
         <v>79917</v>
@@ -7380,14 +7410,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gängesmyran Asplövberg, Nb</t>
+          <t>Gängesmyran Asplövberget, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>782137</v>
+        <v>782565</v>
       </c>
       <c r="R66" t="n">
-        <v>7290681</v>
+        <v>7290181</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7434,27 +7464,27 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125141673</t>
+          <t>https://artportalen.se/Sighting/124791540</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124754554</v>
+        <v>125141672</v>
       </c>
       <c r="B67" t="n">
-        <v>79350</v>
+        <v>79917</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7462,21 +7492,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7486,10 +7516,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>782326</v>
+        <v>782114</v>
       </c>
       <c r="R67" t="n">
-        <v>7290301</v>
+        <v>7290605</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7546,6 +7576,210 @@
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125141672</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125141673</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>782137</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7290681</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125141673</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>124754554</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gängesmyran Asplövberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>782326</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7290301</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/124754554</t>
         </is>
@@ -7619,6 +7853,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>137247075</v>
       </c>
       <c r="B43" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>137247076</v>
       </c>
       <c r="B44" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>137247075</v>
       </c>
       <c r="B43" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>137247076</v>
       </c>
       <c r="B44" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>137247075</v>
       </c>
       <c r="B43" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>137247076</v>
       </c>
       <c r="B44" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 56243-2024 artfynd.xlsx
+++ b/artfynd/A 56243-2024 artfynd.xlsx
@@ -3470,7 +3470,7 @@
         <v>136898208</v>
       </c>
       <c r="B29" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>137247075</v>
       </c>
       <c r="B43" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>137247076</v>
       </c>
       <c r="B44" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
